--- a/results/tab01.xlsx
+++ b/results/tab01.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,25 +434,35 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>H1(OLS)+geo+country+region</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>H1(RLM)+full</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>H1(RLM)+geo</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>H1(RLM)+geo+country</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>H1(RLM)+geo+country+region</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
         <is>
           <t>H1(MLM)+geo+country</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>H1(MLM)+geo+country+region</t>
         </is>
@@ -484,29 +494,41 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>6.164***
+[6.044, 6.284]</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>5.122***
 [5.078, 5.165]</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>5.755***
 [5.647, 5.862]</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>5.789***
 [5.673, 5.905]</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>6.173***
+[6.052, 6.295]</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
         <is>
           <t>5.718***
 [5.576, 5.861]</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>5.617***
 [5.501, 5.732]</t>
@@ -539,29 +561,41 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>0.077***
+[0.035, 0.119]</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>0.205***
 [0.187, 0.224]</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>0.047*
 [0.004, 0.090]</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>0.047*
 [0.004, 0.090]</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>0.080***
+[0.037, 0.122]</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
         <is>
           <t>0.099***
 [0.058, 0.141]</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>0.136***
 [0.096, 0.176]</t>
@@ -582,43 +616,60 @@
 [-0.002, 0.000]</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>-0.000
+[-0.001, 0.000]</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr">
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
         <is>
           <t>-0.001
 [-0.002, 0.000]</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>-0.001
+[-0.001, 0.000]</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Country Var.</t>
+          <t>Region</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>-0.002***
+[-0.002, -0.002]</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0.105
-(0.024)</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>-0.002***
+[-0.002, -0.002]</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Region Var.</t>
+          <t>Country Var.</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -628,56 +679,92 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>0.144
-(0.019)</t>
-        </is>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>0.105
+(0.024)</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>Region Var.</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0.144
+(0.019)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>R² = .01, R²adj = .01, F(1, 35480) = 469.53, p &lt; .0001, AIC = 106824.3, BIC = 106841.3, LL = -53410.1, MAE = 0.906, MAD = 0.924, N = 35481</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>R² = 0., R²adj = 0., F(1, 7916) = 4.43, p = .035, AIC = 25624.5, BIC = 25638.5, LL = -12810.3, MAE = 1.016, MAD = 1.051, N = 7917</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>R² = 0., R²adj = 0., F(2, 7915) = 3.38, p = .034, AIC = 25624.2, BIC = 25645.1, LL = -12809.1, MAE = 1.015, MAD = 1.060, N = 7917</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>R² = .04, R²adj = .04, F(3, 7914) = 109.04, p &lt; .0001, AIC = 25312.3, BIC = 25340.2, LL = -12652.1, MAE = 0.979, MAD = 0.927, N = 7917</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
         <is>
           <t>R² = .01, R²adj = .01, F(1, 35480) = 477.06, p &lt; .0001, MAE = 0.906, MAD = 0.923, N = 35481</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>R² = 0., R²adj = 0., F(1, 7916) = 4.62, p = .032, MAE = 1.016, MAD = 1.052, N = 7917</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>R² = 0., R²adj = 0., F(2, 7915) = 3.50, p = .030, MAE = 1.015, MAD = 1.059, N = 7917</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>R² = .04, R²adj = .04, F(3, 7914) = 117.38, p &lt; .0001, MAE = 0.978, MAD = 0.923, N = 7917</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
         <is>
           <t>R² = .07, R²adj = .07, F(1, 7916) = 628.02, p &lt; .0001, AIC = 25105.1, BIC = 25133.0, LL = -12548.5, MAE = 0.951, MAD = 0.933, N = 7917, G = 97,
  ICC = 0.07, LRTstat. = 81723.2 (p &lt; .0001)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>R² = .11, R²adj = .11, F(1, 7916) = 958.25, p &lt; .0001, AIC = 24471.1, BIC = 24506.0, LL = -12230.5, MAE = 0.874, MAD = 0.788, N = 7917, G = 97,
  ICC = 0.00, LRTstat. = 81723.2 (p &lt; .0001)</t>

--- a/results/tab01.xlsx
+++ b/results/tab01.xlsx
@@ -476,8 +476,8 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>5.125***
-[5.081, 5.168]</t>
+          <t>5.043***
+[4.996, 5.090]</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -500,8 +500,8 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>5.122***
-[5.078, 5.165]</t>
+          <t>5.038***
+[4.991, 5.085]</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -543,8 +543,8 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.205***
-[0.186, 0.223]</t>
+          <t>0.210***
+[0.189, 0.230]</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -567,8 +567,8 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.205***
-[0.187, 0.224]</t>
+          <t>0.212***
+[0.191, 0.232]</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -720,7 +720,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>R² = .01, R²adj = .01, F(1, 35480) = 469.53, p &lt; .0001, AIC = 106824.3, BIC = 106841.3, LL = -53410.1, MAE = 0.906, MAD = 0.924, N = 35481</t>
+          <t>R² = .01, R²adj = .01, F(1, 27563) = 402.20, p &lt; .0001, AIC = 80273.1, BIC = 80289.6, LL = -40134.6, MAE = 0.867, MAD = 0.879, N = 27564</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -740,7 +740,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>R² = .01, R²adj = .01, F(1, 35480) = 477.06, p &lt; .0001, MAE = 0.906, MAD = 0.923, N = 35481</t>
+          <t>R² = .01, R²adj = .01, F(1, 27563) = 412.13, p &lt; .0001, MAE = 0.867, MAD = 0.878, N = 27564</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">

--- a/results/tab01.xlsx
+++ b/results/tab01.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="B1" t="inlineStr">
         <is>
-          <t>H1(OLS)+full</t>
+          <t>H1(OLS)+nogeo</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
@@ -439,7 +439,7 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>H1(RLM)+full</t>
+          <t>H1(RLM)+nogeo</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
